--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N79_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N79_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>79.49614160189635</v>
+        <v>12.91812301030816</v>
       </c>
       <c r="D2" t="n">
-        <v>80.06231816577326</v>
+        <v>13.01012670193816</v>
       </c>
       <c r="E2" t="n">
-        <v>10.03485710390196</v>
+        <v>1.630664279384068</v>
       </c>
       <c r="F2" t="n">
-        <v>10.28309462656747</v>
+        <v>1.671002876817214</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>65.69106984794587</v>
+        <v>10.6747988502912</v>
       </c>
       <c r="D3" t="n">
-        <v>66.2449402217039</v>
+        <v>10.76480278602688</v>
       </c>
       <c r="E3" t="n">
-        <v>10.03485710390196</v>
+        <v>1.630664279384068</v>
       </c>
       <c r="F3" t="n">
-        <v>10.28309462656747</v>
+        <v>1.671002876817214</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.98089433990145</v>
+        <v>8.934395330233986</v>
       </c>
       <c r="D4" t="n">
-        <v>54.91495577683973</v>
+        <v>8.923680313736456</v>
       </c>
       <c r="E4" t="n">
-        <v>10.03485710390196</v>
+        <v>1.630664279384068</v>
       </c>
       <c r="F4" t="n">
-        <v>10.28309462656747</v>
+        <v>1.671002876817214</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
